--- a/01. xlsx/calender_data.xlsx
+++ b/01. xlsx/calender_data.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="IEIP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Linux" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sqld" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Yuhan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="IEIP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Linux" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sqld" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,154 +416,666 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>division</t>
+          <t>days</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>written_form</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>written_exam</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>written_result_date</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>practical_form</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>practical_exam</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>final_result_date</t>
+          <t>contents</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>제1회</t>
+          <t>01월 01일</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01.12~01.15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>01.30~03.03</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>03.11(수)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>03.23~03.26</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>04.18(토)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>06.12(금)</t>
+          <t>신정</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>제2회</t>
+          <t xml:space="preserve">01월 05일~01월 09일 </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04.20~04.23</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>05.09~05.29</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>06.10(수)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>06.22~06.25</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>07.19(일)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>09.11(금)</t>
+          <t>동계 집중휴무기간(예정)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>제3회</t>
+          <t xml:space="preserve">01월 13일~01월 15일 </t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07.20~07.23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>08.07~09.01</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>09.09(수)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>09.21~09.28</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10.25(일)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>12.18(금)</t>
+          <t>전과 신청, 재입학 신청</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01월 26일~01월 30일 </t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>휴복학기간</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02월 10일~02월 12일 </t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>수강신청</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>02월 12일</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>학위수여식</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02월 16일~02월 18일 </t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>설 연휴</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02월 23일~02월 26일 </t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>등록기간</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02월 24일~02월 25일 </t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>신입생 수강신청</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>02월 26일</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>전 학년 수강신청</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>03월 01일</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>삼일절</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>03월 02일</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>대체공휴일</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>03월 03일</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026학년도 1학기 개강</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>03월 11일</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>설립자 유일한박사 55주기 추모식</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>03월 18일</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>개교기념일(48주년)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>04월 01일</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>수업일수 30일</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>05월 01일</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>근로자의날(보강:6/12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>05월 04일</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>재량 휴업일(보강:6/15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>05월 05일</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>어린이날(보강:6/9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>05월 06일</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>수업일수 60일</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>05월 24일</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>부처님오신날</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>05월 25일</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>대체공휴일(보강:6/16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>06월 01일</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>수업일수 90일</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>06월 03일</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>전국동시지방선거(보강:6/11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>06월 06일</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>현충일</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06월 09일~06월 16일 </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>보강기간</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06월 17일~06월 23일 </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>기말고사</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06월 26일~06월 30일 </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>성적입력 및 강의평가</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07월 01일~07월 03일 </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>성적열람 및 정정, 강의평가</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07월 14일~07월 16일 </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>전과 신청, 재입학 신청</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>07월 17일</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>제헌절</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07월 27일~07월 31일 </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>하계 집중휴무기간(예정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08월 04일~08월 07일 </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>휴복학기간</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08월 10일~08월 14일 </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>수강신청</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>08월 13일</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>후기학위수여식</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>08월 15일</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>광복절</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>08월 17일</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>대체공휴일</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08월 18일~08월 21일 </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>등록기간</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>08월 24일</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-2학기 개강</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>09월 22일</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>수업일수 30일</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>09월 24일</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>추석 연휴(보강:12/3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>09월 25일</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>추석(보강:12/4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>09월 26일</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>추석연휴</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10월 03일</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>개천절</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10월 05일</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>대체공휴일(보강:11/30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10월 09일</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>한글날(보강:12/2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10월 22일</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>수업일수 60일</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>11월 23일</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>수업일수 90일</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11월 30일~12월 04일 </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>보강기간</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11월 30일~12월 04일 </t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>보강기간</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12월 07일~12월 11일 </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>기말고사</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12월 16일~12월 18일 </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>성적입력 및 강의평가</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12월 21일~12월 23일 </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>성적열람 및 정정, 강의평가</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12월 25일</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>성탄절</t>
         </is>
       </c>
     </row>
@@ -577,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,148 +1133,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2601회</t>
+          <t>제1회</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01.26.(월) ~ 02.04.(수)</t>
+          <t>01.12~01.15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01.27.(화) ~ 02.05.(목)</t>
+          <t>01.30~03.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>시험종료 즉시</t>
+          <t>03.11(수)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01.27.(화) ~ 02.06.(금)</t>
+          <t>03.23~03.26</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>03.14.(토)</t>
+          <t>04.18(토)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>04.03.(금)</t>
+          <t>06.12(금)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2602회</t>
+          <t>제2회</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04.06.(월) ~ 04.17.(금)</t>
+          <t>04.20~04.23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>05.02.(토)</t>
+          <t>05.09~05.29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>시험종료 즉시</t>
+          <t>06.10(수)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04.28.(화) ~ 05.08.(금)</t>
+          <t>06.22~06.25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>06.13.(토)</t>
+          <t>07.19(일)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>07.03.(금)</t>
+          <t>09.11(금)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2603회</t>
+          <t>제3회</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07.06.(월) ~ 07.17.(금)</t>
+          <t>07.20~07.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08.01.(토)</t>
+          <t>08.07~09.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>시험종료 즉시</t>
+          <t>09.09(수)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>07.28.(화) ~ 08.07.(금)</t>
+          <t>09.21~09.28</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>09.12.(토)</t>
+          <t>10.25(일)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.09.(금)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2604회</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>10.05.(월) ~ 10.16.(금)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>10.31.(토)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>시험종료 즉시</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10.27.(화) ~ 11.06.(금)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>12.12.(토)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>12.31.(목)</t>
+          <t>12.18(금)</t>
         </is>
       </c>
     </row>
@@ -819,6 +1295,205 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2601회</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01.26.(월) ~ 02.04.(수)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01.27.(화) ~ 02.05.(목)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>시험종료 즉시</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>01.27.(화) ~ 02.06.(금)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>03.14.(토)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>04.03.(금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2602회</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>04.06.(월) ~ 04.17.(금)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>05.02.(토)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>시험종료 즉시</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04.28.(화) ~ 05.08.(금)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>06.13.(토)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>07.03.(금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2603회</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07.06.(월) ~ 07.17.(금)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>08.01.(토)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>시험종료 즉시</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>07.28.(화) ~ 08.07.(금)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>09.12.(토)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10.09.(금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2604회</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10.05.(월) ~ 10.16.(금)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10.31.(토)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>시험종료 즉시</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10.27.(화) ~ 11.06.(금)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>12.12.(토)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>12.31.(목)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>division</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>written_form</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>written_exam</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>written_result_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>practical_form</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>practical_exam</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>final_result_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>제 60회</t>
         </is>
       </c>
